--- a/medford_konsoli_khirurgicheskie.xlsx
+++ b/medford_konsoli_khirurgicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Консоли хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray — всего 20 позиций.</t>
+          <t>Консоли хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_konsoli_khirurgicheskie.xlsx
+++ b/medford_konsoli_khirurgicheskie.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать консоли хирургические для клиники?</t>
+          <t>Что такое хирургическая консоль простыми словами?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это конструкция в операционной, которая собирает в одном месте подводы газов (кислород, вакуум, сжатый воздух), электрические розетки и держатели для приборов у стола. Она убирает провода и шланги с пола и даёт хирургической бригаде быстрый доступ к нужным ресурсам и оборудованию во время операции.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какие бывают виды консолей?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>По креплению различают потолочные (крепятся к перекрытию, поворачиваются, освобождают место вокруг пациента), настенные (жёстко фиксируются на стене, для небольших помещений) и мобильные на колёсах. Отдельно выделяют мостовые конструкции и реанимационные мосты для палат интенсивной терапии.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем потолочная консоль отличается от настенной?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Mindray. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Потолочная крепится к перекрытию и может поворачиваться и перемещаться, освобождая максимум пространства вокруг операционного стола. Настенная жёстко зафиксирована на стене, занимает меньше подготовки и подходит для небольших помещений или зон с фиксированным расположением техники, но не даёт круговой доступ.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что можно разместить на консоли?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>На полках и кронштейнах консоли крепят мониторы пациента, наркозно-дыхательные аппараты, хирургические светильники, эндоскопические стойки и другую аппаратуру. Через посты консоли подводят кислород, вакуум и сжатый воздух, а через разъёмы — электропитание приборов рабочей зоны.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Как рассчитать комплектацию консоли?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Составьте перечень необходимых постов газов и электрических разъёмов исходя из приборов операционной и запаса на развитие, затем определите число и конфигурацию плеч и предельную нагрузку под вес аппаратуры. Точную комплектацию и присоединительные параметры согласуют с поставщиком под конкретное помещение.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что такое консоль простыми словами?</t>
+          <t>Требуется ли особая подготовка помещения?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Потолочные и мостовые консоли устанавливаются на подготовленное перекрытие с заранее разведёнными линиями газов и электрики. До заказа уточняют присоединительные размеры, тип разъёмов газов и совместимость с существующей разводкой. Настенные модели предъявляют меньше требований к перекрытию.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Почему консоль так называется?</t>
+          <t>Какие бренды консолей есть в каталоге?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>В категории представлены консоли CADUCEUS российского производства в потолочном, настенном и мостовом исполнении, одно- и двухплечевые, вертикальные и горизонтальные, а также реанимационный мост Mindray HyPort 8000-I/II. Конкретную модель подбирают под тип помещения и набор подводимых сред.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Консоли хирургические для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray.</t>
+          <t>Хирургические консоли — устройства оснащения операционной, которые объединяют подводы медицинских газов, электрические разъёмы, освещение и полки для приборов у операционного стола. В категории представлены потолочные, настенные и мостовые консоли CADUCEUS (Россия) — одноплечевые и двухплечевые, вертикальные и горизонтальные, а также реанимационный мост Mindray HyPort 8000-I/II (Китай). Консоль убирает провода и шланги с пола, обеспечивает быстрый доступ к кислороду, вакууму и сжатому воздуху и служит платформой для мониторов, наркозных аппаратов и эндоскопических стоек.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы хирургических консолей по креплению</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое консоли хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4364,159 +4364,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы хирургических консолей по креплению</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Потолочная</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
+          <t>Настенная</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Потолочная медицинская консоль CADUCEUS C1-VE одноплечевая</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Крепление</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>К перекрытию</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>67334</t>
+          <t>К стене</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Реанимационный мост Mindray HyPort 8000-I/II</t>
+          <t>Подвижность</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>Поворот и перемещение</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1213</t>
+          <t>Жёсткая фиксация</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Мостовая медицинская консоль CADUCEUS CBN4</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>Место вокруг пациента</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Максимально свободно</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>67334</t>
+          <t>Ограничено зоной у стены</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Потолочная медицинская консоль CADUCEUS CC-VE</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
+          <t>Подходит для</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Операционных</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>67334</t>
+          <t>Небольших помещений, процедурных</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Потолочная медицинская консоль CADUCEUS CC-A</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>Пример из каталога</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CADUCEUS C1/C2 потолочные</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>67334</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Потолочная медицинская консоль CADUCEUS C2-A двухплечевая</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>67334</t>
+          <t>CADUCEUS CN1, CN2, CN3-2</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4528,7 +4495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4854,12 +4821,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип помещения</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается консоли хирургические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Операционная, реанимация, палата интенсивной терапии и процедурный кабинет предъявляют разные требования. Для операционной берут потолочную поворотную консоль, для реанимации — реанимационный мост, для небольших помещений — настенную модель.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4899,12 +4866,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите способ крепления</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Потолочные консоли CADUCEUS крепятся к перекрытию, поворачиваются и освобождают максимум места вокруг пациента. Настенные жёстко фиксируются на стене и подходят зонам с фиксированным расположением техники. Мостовые конструкции перекрывают рабочую зону сверху.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4944,12 +4911,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Рассчитайте подводимые среды</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Составьте перечень постов: кислород, вакуум, сжатый воздух, при необходимости — закись азота и другие газы. Число розеток газов и электрических разъёмов должно покрывать текущие приборы и запас на развитие. Это ключевой параметр комплектации консоли.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4989,12 +4956,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Определите конфигурацию плеч</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Mindray.</t>
+          <t>Одноплечевые модели (CADUCEUS C1-серия) проще и легче, двухплечевые (C2-серия) распределяют нагрузку и дают больше точек размещения. Вертикальное или горизонтальное исполнение выбирают под планировку и высоту потолка операционной.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5034,12 +5001,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте нагрузку и держатели</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>На полках и кронштейнах крепят мониторы, наркозные аппараты, светильники и эндоскопические стойки. Сверьте предельную нагрузку на плечо и полку с весом планируемой аппаратуры, наличие регулировки по высоте и креплений под ваши приборы.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5079,12 +5046,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Согласуйте требования к установке</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Потолочная и мостовая консоль требуют подготовленного перекрытия и заранее разведённых линий газов и электрики. Уточните у поставщика присоединительные размеры, тип разъёмов газов (стандарт клиники) и совместимость с существующей разводкой до заказа.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5134,7 +5101,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Консоли хирургические подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Mindray. При выборе обращают внимание на страна производства, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Выбор консоли начинается с профиля помещения и набора подводимых сред. Потолочные модели CADUCEUS с поворотными плечами освобождают зону вокруг стола и удобны в операционных, настенные — компактное решение для процедурных и небольших кабинетов, мостовые и реанимационные мосты вроде Mindray HyPort рассчитаны на реанимацию и палаты интенсивной терапии. Заранее считайте число постов газов, электрических разъёмов и предельную нагрузку на плечо под мониторы и аппаратуру.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5418,13 +5385,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое консоли хирургические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Консоли хирургические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Mindray. Подберём вариант под задачи вашего отделения.</t>
+          <t>Хирургическая консоль — устройство для операционной, объединяющее розетки медицинских газов, электропитание и держатели для приборов у стола. По креплению различают потолочные (поворотные, освобождают место вокруг пациента), настенные (жёстко фиксируются, для небольших помещений) и мостовые конструкции, а также реанимационные мосты для палат интенсивной терапии. В каталоге — консоли CADUCEUS российского производства (одно- и двухплечевые, потолочные, настенные, мостовые, вертикальные и горизонтальные) и реанимационный мост Mindray HyPort 8000-I/II. Консоль организует пространство и подаёт газы, вакуум и электричество к рабочей зоне.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5461,13 +5428,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое хирургическая консоль</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Хирургическая консоль — элемент оснащения операционной, объединяющий подводы медицинских газов, электрические разъёмы и держатели для приборов у операционного стола. Она организует рабочее пространство, убирает провода и шланги с пола, снижая риск споткнуться, и обеспечивает бригаде быстрый доступ к кислороду, вакууму, сжатому воздуху и электросети.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5504,13 +5471,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Виды хирургических консолей</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По способу крепления консоли делят на потолочные, настенные и мобильные. Потолочные крепятся к перекрытию, поворачиваются и освобождают место вокруг пациента. Настенные жёстко фиксируются на стене и подходят для небольших помещений. Мобильные на колёсах перемещают между залами. Отдельно выделяют мостовые конструкции и реанимационные мосты.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5547,13 +5514,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Что размещают на консоли</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>На полках и кронштейнах консоли крепят мониторы, наркозные аппараты, хирургические светильники и эндоскопические стойки. Посты консоли подают кислород, вакуум и сжатый воздух прямо у стола, а электрические разъёмы питают приборы рабочей зоны. Вертикальная организация секций компактно размещает оборудование и освобождает пол операционной.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5570,6 +5537,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать консоль под операционную</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Отталкивайтесь от типа помещения и набора подводимых сред: для операционной — потолочная поворотная консоль, для реанимации — реанимационный мост, для небольших зон — настенная модель. Считайте число постов газов и разъёмов, конфигурацию плеч и предельную нагрузку под вес аппаратуры, а параметры установки согласуйте с поставщиком.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>konsoli_khirurgicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
